--- a/data/nzd0060/nzd0060.xlsx
+++ b/data/nzd0060/nzd0060.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J240"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9080,6 +9080,42 @@
         <v>383.38</v>
       </c>
       <c r="J240" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>387.15</v>
+      </c>
+      <c r="C241" t="n">
+        <v>401.01</v>
+      </c>
+      <c r="D241" t="n">
+        <v>391.96</v>
+      </c>
+      <c r="E241" t="n">
+        <v>387.27</v>
+      </c>
+      <c r="F241" t="n">
+        <v>375.47</v>
+      </c>
+      <c r="G241" t="n">
+        <v>369.06</v>
+      </c>
+      <c r="H241" t="n">
+        <v>380.41</v>
+      </c>
+      <c r="I241" t="n">
+        <v>383.17</v>
+      </c>
+      <c r="J241" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9096,7 +9132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11629,6 +11665,16 @@
       </c>
       <c r="B253" t="n">
         <v>0.86</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -11797,28 +11843,28 @@
         <v>0.0403</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07489123946608255</v>
+        <v>-0.07687095880390737</v>
       </c>
       <c r="J2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01152208207547845</v>
+        <v>0.0122255928999514</v>
       </c>
       <c r="M2" t="n">
-        <v>4.048786398540371</v>
+        <v>4.041422558287769</v>
       </c>
       <c r="N2" t="n">
-        <v>29.51950656253286</v>
+        <v>29.42404971426576</v>
       </c>
       <c r="O2" t="n">
-        <v>5.433185673482258</v>
+        <v>5.424393949029307</v>
       </c>
       <c r="P2" t="n">
-        <v>391.7054761180091</v>
+        <v>391.7242815647064</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11879,28 +11925,28 @@
         <v>0.0251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05324603756950797</v>
+        <v>-0.05864104989361974</v>
       </c>
       <c r="J3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K3" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004030554727707192</v>
+        <v>0.004903821504113948</v>
       </c>
       <c r="M3" t="n">
-        <v>4.950327334070749</v>
+        <v>4.951864798926497</v>
       </c>
       <c r="N3" t="n">
-        <v>42.98004154690704</v>
+        <v>43.0054889014988</v>
       </c>
       <c r="O3" t="n">
-        <v>6.555916529891685</v>
+        <v>6.55785703576243</v>
       </c>
       <c r="P3" t="n">
-        <v>409.4565887891884</v>
+        <v>409.5078362638953</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -11961,28 +12007,28 @@
         <v>0.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3765136820633915</v>
+        <v>-0.3845049874597194</v>
       </c>
       <c r="J4" t="n">
+        <v>240</v>
+      </c>
+      <c r="K4" t="n">
         <v>239</v>
       </c>
-      <c r="K4" t="n">
-        <v>238</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1374268421921473</v>
+        <v>0.1425565493647296</v>
       </c>
       <c r="M4" t="n">
-        <v>5.864305921468693</v>
+        <v>5.878802009519108</v>
       </c>
       <c r="N4" t="n">
-        <v>54.71460504957439</v>
+        <v>54.93291759212019</v>
       </c>
       <c r="O4" t="n">
-        <v>7.396932137688867</v>
+        <v>7.411674412177062</v>
       </c>
       <c r="P4" t="n">
-        <v>412.2539162942817</v>
+        <v>412.3296338319489</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12043,28 +12089,28 @@
         <v>0.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.134895958926734</v>
+        <v>-1.135704793889346</v>
       </c>
       <c r="J5" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K5" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5330966302836762</v>
+        <v>0.5356072866863308</v>
       </c>
       <c r="M5" t="n">
-        <v>6.53605391869633</v>
+        <v>6.512797508782866</v>
       </c>
       <c r="N5" t="n">
-        <v>69.20607513591544</v>
+        <v>68.92231369372807</v>
       </c>
       <c r="O5" t="n">
-        <v>8.319018880608184</v>
+        <v>8.301946379839373</v>
       </c>
       <c r="P5" t="n">
-        <v>418.1278924698067</v>
+        <v>418.1355756309931</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12125,28 +12171,28 @@
         <v>0.0429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.395143089130952</v>
+        <v>-1.395176597053538</v>
       </c>
       <c r="J6" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K6" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6076850697212386</v>
+        <v>0.609776272252313</v>
       </c>
       <c r="M6" t="n">
-        <v>6.89767018883579</v>
+        <v>6.869073802274615</v>
       </c>
       <c r="N6" t="n">
-        <v>77.0912032281113</v>
+        <v>76.76999777118159</v>
       </c>
       <c r="O6" t="n">
-        <v>8.780159635684951</v>
+        <v>8.761848992717324</v>
       </c>
       <c r="P6" t="n">
-        <v>412.1478534674186</v>
+        <v>412.1481717607444</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12203,28 +12249,28 @@
         <v>0.0467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.16313426053012</v>
+        <v>-1.164998390199258</v>
       </c>
       <c r="J7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5443448508745157</v>
+        <v>0.5472160694992303</v>
       </c>
       <c r="M7" t="n">
-        <v>6.500075047896211</v>
+        <v>6.480731652599063</v>
       </c>
       <c r="N7" t="n">
-        <v>69.47569651387516</v>
+        <v>69.21063335099443</v>
       </c>
       <c r="O7" t="n">
-        <v>8.335208246581196</v>
+        <v>8.319292839598473</v>
       </c>
       <c r="P7" t="n">
-        <v>402.0465825910886</v>
+        <v>402.0642900461102</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12281,28 +12327,28 @@
         <v>0.0453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9544372880023805</v>
+        <v>-0.9571342652896263</v>
       </c>
       <c r="J8" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K8" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4183978548119468</v>
+        <v>0.4217389896492417</v>
       </c>
       <c r="M8" t="n">
-        <v>6.678646059912261</v>
+        <v>6.661815008108122</v>
       </c>
       <c r="N8" t="n">
-        <v>77.68593486251997</v>
+        <v>77.41335613425758</v>
       </c>
       <c r="O8" t="n">
-        <v>8.813962494957643</v>
+        <v>8.798486013755866</v>
       </c>
       <c r="P8" t="n">
-        <v>408.9966981827424</v>
+        <v>409.0223168962892</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12359,28 +12405,28 @@
         <v>0.0442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.539682063277651</v>
+        <v>-0.5435797623902566</v>
       </c>
       <c r="J9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2224854626252651</v>
+        <v>0.2262109613285775</v>
       </c>
       <c r="M9" t="n">
-        <v>6.111129372849899</v>
+        <v>6.107558321353221</v>
       </c>
       <c r="N9" t="n">
-        <v>62.44445750402588</v>
+        <v>62.29102784454244</v>
       </c>
       <c r="O9" t="n">
-        <v>7.902180553747546</v>
+        <v>7.892466524765401</v>
       </c>
       <c r="P9" t="n">
-        <v>402.4395891317324</v>
+        <v>402.4766135581264</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12418,7 +12464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J240"/>
+  <dimension ref="A1:J241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24897,6 +24943,58 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>-35.17160996337242,173.0953853727716</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>-35.171943733855514,173.096184249941</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-35.17239355458818,173.09684783585493</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-35.17272317706258,173.0976120025946</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-35.17305300243413,173.09837457542613</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-35.17313265141148,173.09924930137768</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-35.173043771926416,173.10012763635757</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-35.17288169782955,173.10098385365043</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0060/nzd0060.xlsx
+++ b/data/nzd0060/nzd0060.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J241"/>
+  <dimension ref="A1:J243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9118,6 +9118,78 @@
       <c r="J241" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="C242" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="D242" t="n">
+        <v>392.95</v>
+      </c>
+      <c r="E242" t="n">
+        <v>387.87</v>
+      </c>
+      <c r="F242" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="G242" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="H242" t="n">
+        <v>380.56</v>
+      </c>
+      <c r="I242" t="n">
+        <v>383.79</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="C243" t="n">
+        <v>402.49</v>
+      </c>
+      <c r="D243" t="n">
+        <v>393.37</v>
+      </c>
+      <c r="E243" t="n">
+        <v>387.15</v>
+      </c>
+      <c r="F243" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="G243" t="n">
+        <v>368.82</v>
+      </c>
+      <c r="H243" t="n">
+        <v>380.37</v>
+      </c>
+      <c r="I243" t="n">
+        <v>384.44</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B254"/>
+  <dimension ref="A1:B256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11675,6 +11747,26 @@
       </c>
       <c r="B254" t="n">
         <v>1.03</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -11843,28 +11935,28 @@
         <v>0.0403</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07687095880390737</v>
+        <v>-0.08143390213505025</v>
       </c>
       <c r="J2" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K2" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0122255928999514</v>
+        <v>0.01389873155891241</v>
       </c>
       <c r="M2" t="n">
-        <v>4.041422558287769</v>
+        <v>4.030810118094283</v>
       </c>
       <c r="N2" t="n">
-        <v>29.42404971426576</v>
+        <v>29.25556658267757</v>
       </c>
       <c r="O2" t="n">
-        <v>5.424393949029307</v>
+        <v>5.408841519463994</v>
       </c>
       <c r="P2" t="n">
-        <v>391.7242815647064</v>
+        <v>391.7677444094728</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -11925,28 +12017,28 @@
         <v>0.0251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05864104989361974</v>
+        <v>-0.06698525385475615</v>
       </c>
       <c r="J3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004903821504113948</v>
+        <v>0.006461585502520295</v>
       </c>
       <c r="M3" t="n">
-        <v>4.951864798926497</v>
+        <v>4.945917276070545</v>
       </c>
       <c r="N3" t="n">
-        <v>43.0054889014988</v>
+        <v>42.89983823636741</v>
       </c>
       <c r="O3" t="n">
-        <v>6.55785703576243</v>
+        <v>6.549796808784789</v>
       </c>
       <c r="P3" t="n">
-        <v>409.5078362638953</v>
+        <v>409.5873163216705</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12007,28 +12099,28 @@
         <v>0.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3845049874597194</v>
+        <v>-0.3981245178809043</v>
       </c>
       <c r="J4" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K4" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1425565493647296</v>
+        <v>0.1519459503083395</v>
       </c>
       <c r="M4" t="n">
-        <v>5.878802009519108</v>
+        <v>5.89814451431395</v>
       </c>
       <c r="N4" t="n">
-        <v>54.93291759212019</v>
+        <v>55.14052218915406</v>
       </c>
       <c r="O4" t="n">
-        <v>7.411674412177062</v>
+        <v>7.42566644747487</v>
       </c>
       <c r="P4" t="n">
-        <v>412.3296338319489</v>
+        <v>412.459033682628</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12089,28 +12181,28 @@
         <v>0.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.135704793889346</v>
+        <v>-1.136810136934788</v>
       </c>
       <c r="J5" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K5" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5356072866863308</v>
+        <v>0.5403441116654089</v>
       </c>
       <c r="M5" t="n">
-        <v>6.512797508782866</v>
+        <v>6.464332455381145</v>
       </c>
       <c r="N5" t="n">
-        <v>68.92231369372807</v>
+        <v>68.35809499907143</v>
       </c>
       <c r="O5" t="n">
-        <v>8.301946379839373</v>
+        <v>8.267895439534261</v>
       </c>
       <c r="P5" t="n">
-        <v>418.1355756309931</v>
+        <v>418.1461071297899</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12171,28 +12263,28 @@
         <v>0.0429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.395176597053538</v>
+        <v>-1.394309729304607</v>
       </c>
       <c r="J6" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K6" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L6" t="n">
-        <v>0.609776272252313</v>
+        <v>0.6135542258761568</v>
       </c>
       <c r="M6" t="n">
-        <v>6.869073802274615</v>
+        <v>6.817950681416599</v>
       </c>
       <c r="N6" t="n">
-        <v>76.76999777118159</v>
+        <v>76.13875971812458</v>
       </c>
       <c r="O6" t="n">
-        <v>8.761848992717324</v>
+        <v>8.725752673444543</v>
       </c>
       <c r="P6" t="n">
-        <v>412.1481717607444</v>
+        <v>412.1399125727743</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12249,28 +12341,28 @@
         <v>0.0467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.164998390199258</v>
+        <v>-1.168922995940556</v>
       </c>
       <c r="J7" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K7" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5472160694992303</v>
+        <v>0.5529360936646762</v>
       </c>
       <c r="M7" t="n">
-        <v>6.480731652599063</v>
+        <v>6.443278875163276</v>
       </c>
       <c r="N7" t="n">
-        <v>69.21063335099443</v>
+        <v>68.6938954791152</v>
       </c>
       <c r="O7" t="n">
-        <v>8.319292839598473</v>
+        <v>8.288178055466425</v>
       </c>
       <c r="P7" t="n">
-        <v>402.0642900461102</v>
+        <v>402.1016726526221</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12327,28 +12419,28 @@
         <v>0.0453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9571342652896263</v>
+        <v>-0.9621887841263225</v>
       </c>
       <c r="J8" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K8" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4217389896492417</v>
+        <v>0.4282223781427701</v>
       </c>
       <c r="M8" t="n">
-        <v>6.661815008108122</v>
+        <v>6.62706218312854</v>
       </c>
       <c r="N8" t="n">
-        <v>77.41335613425758</v>
+        <v>76.86525049345313</v>
       </c>
       <c r="O8" t="n">
-        <v>8.798486013755866</v>
+        <v>8.767282959586346</v>
       </c>
       <c r="P8" t="n">
-        <v>409.0223168962892</v>
+        <v>409.0704632499818</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12405,28 +12497,28 @@
         <v>0.0442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5435797623902566</v>
+        <v>-0.5496581287862425</v>
       </c>
       <c r="J9" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K9" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2262109613285775</v>
+        <v>0.2328017580560825</v>
       </c>
       <c r="M9" t="n">
-        <v>6.107558321353221</v>
+        <v>6.090832527869665</v>
       </c>
       <c r="N9" t="n">
-        <v>62.29102784454244</v>
+        <v>61.90964658956169</v>
       </c>
       <c r="O9" t="n">
-        <v>7.892466524765401</v>
+        <v>7.868268334872782</v>
       </c>
       <c r="P9" t="n">
-        <v>402.4766135581264</v>
+        <v>402.5345089959313</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12464,7 +12556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J241"/>
+  <dimension ref="A1:J243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24995,6 +25087,110 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>-35.171613930518575,173.09538174815088</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>-35.17193420103573,173.09619236795442</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-35.1723857277404,173.0968530644697</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-35.172718155008944,173.09761445364234</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-35.173050342015365,173.0983751720918</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-35.1731353557617,173.09924922115135</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-35.173042424604276,173.10012749130453</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-35.17287621098439,173.10098254768803</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>-35.17161313708936,173.09538247307506</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>-35.17193279697695,173.09619356363066</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-35.17238240725945,173.09685528266962</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-35.1727241814733,173.09761151238501</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-35.17304608534531,173.09837612675676</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-35.17313481489166,173.0992492371966</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-35.173044131212315,173.10012767503838</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-35.17287045864668,173.10098117853414</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0060/nzd0060.xlsx
+++ b/data/nzd0060/nzd0060.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J243"/>
+  <dimension ref="A1:J246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9188,6 +9188,114 @@
         <v>384.44</v>
       </c>
       <c r="J243" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="C244" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="D244" t="n">
+        <v>392.75</v>
+      </c>
+      <c r="E244" t="n">
+        <v>384.28</v>
+      </c>
+      <c r="F244" t="n">
+        <v>373.82</v>
+      </c>
+      <c r="G244" t="n">
+        <v>367.6</v>
+      </c>
+      <c r="H244" t="n">
+        <v>379.56</v>
+      </c>
+      <c r="I244" t="n">
+        <v>383.43</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>386.17</v>
+      </c>
+      <c r="C245" t="n">
+        <v>399.65</v>
+      </c>
+      <c r="D245" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="E245" t="n">
+        <v>384.33</v>
+      </c>
+      <c r="F245" t="n">
+        <v>373.47</v>
+      </c>
+      <c r="G245" t="n">
+        <v>367.68</v>
+      </c>
+      <c r="H245" t="n">
+        <v>379.64</v>
+      </c>
+      <c r="I245" t="n">
+        <v>383.85</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>385.74</v>
+      </c>
+      <c r="C246" t="n">
+        <v>398.34</v>
+      </c>
+      <c r="D246" t="n">
+        <v>391.22</v>
+      </c>
+      <c r="E246" t="n">
+        <v>383.32</v>
+      </c>
+      <c r="F246" t="n">
+        <v>372.68</v>
+      </c>
+      <c r="G246" t="n">
+        <v>367.37</v>
+      </c>
+      <c r="H246" t="n">
+        <v>379.14</v>
+      </c>
+      <c r="I246" t="n">
+        <v>383.65</v>
+      </c>
+      <c r="J246" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9204,7 +9312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B256"/>
+  <dimension ref="A1:B259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11767,6 +11875,36 @@
       </c>
       <c r="B256" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -11935,28 +12073,28 @@
         <v>0.0403</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08143390213505025</v>
+        <v>-0.08981658795271925</v>
       </c>
       <c r="J2" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K2" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01389873155891241</v>
+        <v>0.0171747229959397</v>
       </c>
       <c r="M2" t="n">
-        <v>4.030810118094283</v>
+        <v>4.024170417919049</v>
       </c>
       <c r="N2" t="n">
-        <v>29.25556658267757</v>
+        <v>29.07286258149218</v>
       </c>
       <c r="O2" t="n">
-        <v>5.408841519463994</v>
+        <v>5.391925683973415</v>
       </c>
       <c r="P2" t="n">
-        <v>391.7677444094728</v>
+        <v>391.8479011711605</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12017,28 +12155,28 @@
         <v>0.0251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06698525385475615</v>
+        <v>-0.08551442701230821</v>
       </c>
       <c r="J3" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K3" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006461585502520295</v>
+        <v>0.01054042798796051</v>
       </c>
       <c r="M3" t="n">
-        <v>4.945917276070545</v>
+        <v>4.966682945299341</v>
       </c>
       <c r="N3" t="n">
-        <v>42.89983823636741</v>
+        <v>43.23213693826914</v>
       </c>
       <c r="O3" t="n">
-        <v>6.549796808784789</v>
+        <v>6.57511497528896</v>
       </c>
       <c r="P3" t="n">
-        <v>409.5873163216705</v>
+        <v>409.7645145386096</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12099,28 +12237,28 @@
         <v>0.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3981245178809043</v>
+        <v>-0.4197959514654753</v>
       </c>
       <c r="J4" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1519459503083395</v>
+        <v>0.1666723365506529</v>
       </c>
       <c r="M4" t="n">
-        <v>5.89814451431395</v>
+        <v>5.938255375024448</v>
       </c>
       <c r="N4" t="n">
-        <v>55.14052218915406</v>
+        <v>55.6288315173372</v>
       </c>
       <c r="O4" t="n">
-        <v>7.42566644747487</v>
+        <v>7.458473806170884</v>
       </c>
       <c r="P4" t="n">
-        <v>412.459033682628</v>
+        <v>412.6657555556036</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12181,28 +12319,28 @@
         <v>0.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.136810136934788</v>
+        <v>-1.145893947460873</v>
       </c>
       <c r="J5" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K5" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5403441116654089</v>
+        <v>0.5497478566797993</v>
       </c>
       <c r="M5" t="n">
-        <v>6.464332455381145</v>
+        <v>6.428889827405061</v>
       </c>
       <c r="N5" t="n">
-        <v>68.35809499907143</v>
+        <v>67.72814940178969</v>
       </c>
       <c r="O5" t="n">
-        <v>8.267895439534261</v>
+        <v>8.229711380224078</v>
       </c>
       <c r="P5" t="n">
-        <v>418.1461071297899</v>
+        <v>418.2329782785991</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12263,28 +12401,28 @@
         <v>0.0429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.394309729304607</v>
+        <v>-1.398706295910806</v>
       </c>
       <c r="J6" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K6" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6135542258761568</v>
+        <v>0.6208061735327652</v>
       </c>
       <c r="M6" t="n">
-        <v>6.817950681416599</v>
+        <v>6.754146709540428</v>
       </c>
       <c r="N6" t="n">
-        <v>76.13875971812458</v>
+        <v>75.25691383728494</v>
       </c>
       <c r="O6" t="n">
-        <v>8.725752673444543</v>
+        <v>8.675074284251687</v>
       </c>
       <c r="P6" t="n">
-        <v>412.1399125727743</v>
+        <v>412.1819634020353</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12341,28 +12479,28 @@
         <v>0.0467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.168922995940556</v>
+        <v>-1.176995473758945</v>
       </c>
       <c r="J7" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K7" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5529360936646762</v>
+        <v>0.561928333260715</v>
       </c>
       <c r="M7" t="n">
-        <v>6.443278875163276</v>
+        <v>6.398629289992877</v>
       </c>
       <c r="N7" t="n">
-        <v>68.6938954791152</v>
+        <v>68.01456648211354</v>
       </c>
       <c r="O7" t="n">
-        <v>8.288178055466425</v>
+        <v>8.247094426651943</v>
       </c>
       <c r="P7" t="n">
-        <v>402.1016726526221</v>
+        <v>402.1788671370743</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12419,28 +12557,28 @@
         <v>0.0453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9621887841263225</v>
+        <v>-0.9714066714520814</v>
       </c>
       <c r="J8" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K8" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4282223781427701</v>
+        <v>0.438377666788308</v>
       </c>
       <c r="M8" t="n">
-        <v>6.62706218312854</v>
+        <v>6.583403514635777</v>
       </c>
       <c r="N8" t="n">
-        <v>76.86525049345313</v>
+        <v>76.13532856245301</v>
       </c>
       <c r="O8" t="n">
-        <v>8.767282959586346</v>
+        <v>8.72555606035816</v>
       </c>
       <c r="P8" t="n">
-        <v>409.0704632499818</v>
+        <v>409.1586122832157</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12497,28 +12635,28 @@
         <v>0.0442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5496581287862425</v>
+        <v>-0.5592170287634826</v>
       </c>
       <c r="J9" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K9" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2328017580560825</v>
+        <v>0.2429242564956113</v>
       </c>
       <c r="M9" t="n">
-        <v>6.090832527869665</v>
+        <v>6.068328600848157</v>
       </c>
       <c r="N9" t="n">
-        <v>61.90964658956169</v>
+        <v>61.37865098022538</v>
       </c>
       <c r="O9" t="n">
-        <v>7.868268334872782</v>
+        <v>7.834452819452382</v>
       </c>
       <c r="P9" t="n">
-        <v>402.5345089959313</v>
+        <v>402.6259139971748</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12556,7 +12694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J243"/>
+  <dimension ref="A1:J246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25191,6 +25329,162 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>-35.17162251397992,173.0953739057885</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>-35.171951345331365,173.09617776811496</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>-35.17238730892178,173.09685200818396</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-35.17274820362904,173.09759978820216</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-35.17306763473727,173.09837129376433</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-35.17314581258255,173.09924891094275</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-35.173051406751824,173.1001284583247</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-35.17287939689449,173.10098330598876</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>-35.171617032105516,173.09537891435625</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>-35.17195378395948,173.09617569141315</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>-35.17239189434776,173.0968489449551</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-35.1727477851246,173.09759999245625</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-35.17307073855913,173.09837059765408</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-35.173145091422484,173.09924893233645</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-35.17305068818002,173.10012838096307</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-35.172875679999365,173.1009824213046</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-35.17162013369238,173.0953760805614</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>-35.17196346457375,173.09616744753512</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>-35.17239940495911,173.09684392759678</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-35.17275623891431,173.0975958665227</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-35.17307774432846,173.09836902643363</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-35.17314788591772,173.09924884943587</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-35.17305517925377,173.10012886447322</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-35.17287744994943,173.10098284258277</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0060/nzd0060.xlsx
+++ b/data/nzd0060/nzd0060.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J246"/>
+  <dimension ref="A1:J247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9296,6 +9296,42 @@
         <v>383.65</v>
       </c>
       <c r="J246" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>384.85</v>
+      </c>
+      <c r="C247" t="n">
+        <v>399.36</v>
+      </c>
+      <c r="D247" t="n">
+        <v>392.16</v>
+      </c>
+      <c r="E247" t="n">
+        <v>383.17</v>
+      </c>
+      <c r="F247" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="G247" t="n">
+        <v>367.43</v>
+      </c>
+      <c r="H247" t="n">
+        <v>380.18</v>
+      </c>
+      <c r="I247" t="n">
+        <v>384.93</v>
+      </c>
+      <c r="J247" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9312,7 +9348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11905,6 +11941,16 @@
       </c>
       <c r="B259" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>
@@ -12073,28 +12119,28 @@
         <v>0.0403</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08981658795271925</v>
+        <v>-0.09318597951572657</v>
       </c>
       <c r="J2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0171747229959397</v>
+        <v>0.01856181726075457</v>
       </c>
       <c r="M2" t="n">
-        <v>4.024170417919049</v>
+        <v>4.02491252234601</v>
       </c>
       <c r="N2" t="n">
-        <v>29.07286258149218</v>
+        <v>29.04010159980954</v>
       </c>
       <c r="O2" t="n">
-        <v>5.391925683973415</v>
+        <v>5.388886860921236</v>
       </c>
       <c r="P2" t="n">
-        <v>391.8479011711605</v>
+        <v>391.8804478204705</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12155,28 +12201,28 @@
         <v>0.0251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08551442701230821</v>
+        <v>-0.09145140277326823</v>
       </c>
       <c r="J3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01054042798796051</v>
+        <v>0.01206312652659947</v>
       </c>
       <c r="M3" t="n">
-        <v>4.966682945299341</v>
+        <v>4.972591915587846</v>
       </c>
       <c r="N3" t="n">
-        <v>43.23213693826914</v>
+        <v>43.32160917284731</v>
       </c>
       <c r="O3" t="n">
-        <v>6.57511497528896</v>
+        <v>6.581915311886602</v>
       </c>
       <c r="P3" t="n">
-        <v>409.7645145386096</v>
+        <v>409.8218627762487</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12237,28 +12283,28 @@
         <v>0.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4197959514654753</v>
+        <v>-0.426646851783683</v>
       </c>
       <c r="J4" t="n">
+        <v>246</v>
+      </c>
+      <c r="K4" t="n">
         <v>245</v>
       </c>
-      <c r="K4" t="n">
-        <v>244</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1666723365506529</v>
+        <v>0.1715125614703554</v>
       </c>
       <c r="M4" t="n">
-        <v>5.938255375024448</v>
+        <v>5.949938751540568</v>
       </c>
       <c r="N4" t="n">
-        <v>55.6288315173372</v>
+        <v>55.75400359792206</v>
       </c>
       <c r="O4" t="n">
-        <v>7.458473806170884</v>
+        <v>7.46686035746766</v>
       </c>
       <c r="P4" t="n">
-        <v>412.6657555556036</v>
+        <v>412.7317657146857</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12319,28 +12365,28 @@
         <v>0.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.145893947460873</v>
+        <v>-1.149247249028425</v>
       </c>
       <c r="J5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5497478566797993</v>
+        <v>0.5529540512805748</v>
       </c>
       <c r="M5" t="n">
-        <v>6.428889827405061</v>
+        <v>6.418667147949034</v>
       </c>
       <c r="N5" t="n">
-        <v>67.72814940178969</v>
+        <v>67.53743922317999</v>
       </c>
       <c r="O5" t="n">
-        <v>8.229711380224078</v>
+        <v>8.218116525286069</v>
       </c>
       <c r="P5" t="n">
-        <v>418.2329782785991</v>
+        <v>418.2653695065431</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12401,28 +12447,28 @@
         <v>0.0429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.398706295910806</v>
+        <v>-1.400231030954426</v>
       </c>
       <c r="J6" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K6" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6208061735327652</v>
+        <v>0.6232317069368782</v>
       </c>
       <c r="M6" t="n">
-        <v>6.754146709540428</v>
+        <v>6.733638896523554</v>
       </c>
       <c r="N6" t="n">
-        <v>75.25691383728494</v>
+        <v>74.96848394465032</v>
       </c>
       <c r="O6" t="n">
-        <v>8.675074284251687</v>
+        <v>8.658434266346909</v>
       </c>
       <c r="P6" t="n">
-        <v>412.1819634020353</v>
+        <v>412.1966915853964</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12479,28 +12525,28 @@
         <v>0.0467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.176995473758945</v>
+        <v>-1.179515242982283</v>
       </c>
       <c r="J7" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K7" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L7" t="n">
-        <v>0.561928333260715</v>
+        <v>0.5648660725723084</v>
       </c>
       <c r="M7" t="n">
-        <v>6.398629289992877</v>
+        <v>6.383154025238567</v>
       </c>
       <c r="N7" t="n">
-        <v>68.01456648211354</v>
+        <v>67.78585779804085</v>
       </c>
       <c r="O7" t="n">
-        <v>8.247094426651943</v>
+        <v>8.233216734547977</v>
       </c>
       <c r="P7" t="n">
-        <v>402.1788671370743</v>
+        <v>402.2032068564927</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12557,28 +12603,28 @@
         <v>0.0453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9714066714520814</v>
+        <v>-0.9737039070847274</v>
       </c>
       <c r="J8" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K8" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L8" t="n">
-        <v>0.438377666788308</v>
+        <v>0.441475159680732</v>
       </c>
       <c r="M8" t="n">
-        <v>6.583403514635777</v>
+        <v>6.565863804323994</v>
       </c>
       <c r="N8" t="n">
-        <v>76.13532856245301</v>
+        <v>75.86554305732086</v>
       </c>
       <c r="O8" t="n">
-        <v>8.72555606035816</v>
+        <v>8.710082838717486</v>
       </c>
       <c r="P8" t="n">
-        <v>409.1586122832157</v>
+        <v>409.1808024386548</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12635,28 +12681,28 @@
         <v>0.0442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5592170287634826</v>
+        <v>-0.5612844804661888</v>
       </c>
       <c r="J9" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K9" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2429242564956113</v>
+        <v>0.2457353344152055</v>
       </c>
       <c r="M9" t="n">
-        <v>6.068328600848157</v>
+        <v>6.054835228859977</v>
       </c>
       <c r="N9" t="n">
-        <v>61.37865098022538</v>
+        <v>61.16130562809265</v>
       </c>
       <c r="O9" t="n">
-        <v>7.834452819452382</v>
+        <v>7.820569392831486</v>
       </c>
       <c r="P9" t="n">
-        <v>402.6259139971748</v>
+        <v>402.6458845539578</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12694,7 +12740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J246"/>
+  <dimension ref="A1:J247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25485,6 +25531,58 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>-35.171626553255656,173.09537021526447</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>-35.17195592699627,173.09617386643268</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>-35.17239197340683,173.09684889214083</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-35.17275749442763,173.09759525376026</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-35.17307579335472,173.09836946398872</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-35.173147345047674,173.09924886548114</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-35.17304583782036,173.10012785877217</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-35.17286612226901,173.10098014640283</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0060/nzd0060.xlsx
+++ b/data/nzd0060/nzd0060.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J247"/>
+  <dimension ref="A1:J249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9332,6 +9332,78 @@
         <v>384.93</v>
       </c>
       <c r="J247" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>384.53</v>
+      </c>
+      <c r="C248" t="n">
+        <v>399.58</v>
+      </c>
+      <c r="D248" t="n">
+        <v>393.2</v>
+      </c>
+      <c r="E248" t="n">
+        <v>383.09</v>
+      </c>
+      <c r="F248" t="n">
+        <v>373.25</v>
+      </c>
+      <c r="G248" t="n">
+        <v>368</v>
+      </c>
+      <c r="H248" t="n">
+        <v>380.26</v>
+      </c>
+      <c r="I248" t="n">
+        <v>385.9</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>385.28</v>
+      </c>
+      <c r="C249" t="n">
+        <v>400.86</v>
+      </c>
+      <c r="D249" t="n">
+        <v>393.79</v>
+      </c>
+      <c r="E249" t="n">
+        <v>384.58</v>
+      </c>
+      <c r="F249" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="G249" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="H249" t="n">
+        <v>380.71</v>
+      </c>
+      <c r="I249" t="n">
+        <v>387.06</v>
+      </c>
+      <c r="J249" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9348,7 +9420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11951,6 +12023,26 @@
       </c>
       <c r="B260" t="n">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -12119,28 +12211,28 @@
         <v>0.0403</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09318597951572657</v>
+        <v>-0.09962410646825093</v>
       </c>
       <c r="J2" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K2" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01856181726075457</v>
+        <v>0.02138701261371401</v>
       </c>
       <c r="M2" t="n">
-        <v>4.02491252234601</v>
+        <v>4.025025447908035</v>
       </c>
       <c r="N2" t="n">
-        <v>29.04010159980954</v>
+        <v>28.96612292836646</v>
       </c>
       <c r="O2" t="n">
-        <v>5.388886860921236</v>
+        <v>5.382018480864447</v>
       </c>
       <c r="P2" t="n">
-        <v>391.8804478204705</v>
+        <v>391.9427998577145</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12201,28 +12293,28 @@
         <v>0.0251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09145140277326823</v>
+        <v>-0.1017114595120385</v>
       </c>
       <c r="J3" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K3" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01206312652659947</v>
+        <v>0.01498301750440145</v>
       </c>
       <c r="M3" t="n">
-        <v>4.972591915587846</v>
+        <v>4.977944732917074</v>
       </c>
       <c r="N3" t="n">
-        <v>43.32160917284731</v>
+        <v>43.37953030056408</v>
       </c>
       <c r="O3" t="n">
-        <v>6.581915311886602</v>
+        <v>6.586313862895093</v>
       </c>
       <c r="P3" t="n">
-        <v>409.8218627762487</v>
+        <v>409.9212285957875</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12283,28 +12375,28 @@
         <v>0.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.426646851783683</v>
+        <v>-0.4379495207167112</v>
       </c>
       <c r="J4" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K4" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1715125614703554</v>
+        <v>0.1802150370339336</v>
       </c>
       <c r="M4" t="n">
-        <v>5.949938751540568</v>
+        <v>5.960469949246783</v>
       </c>
       <c r="N4" t="n">
-        <v>55.75400359792206</v>
+        <v>55.79221423236456</v>
       </c>
       <c r="O4" t="n">
-        <v>7.46686035746766</v>
+        <v>7.469418600692062</v>
       </c>
       <c r="P4" t="n">
-        <v>412.7317657146857</v>
+        <v>412.8409638994842</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12365,28 +12457,28 @@
         <v>0.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.149247249028425</v>
+        <v>-1.154701000263527</v>
       </c>
       <c r="J5" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K5" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5529540512805748</v>
+        <v>0.5589241383786843</v>
       </c>
       <c r="M5" t="n">
-        <v>6.418667147949034</v>
+        <v>6.392452478858062</v>
       </c>
       <c r="N5" t="n">
-        <v>67.53743922317999</v>
+        <v>67.11199525955489</v>
       </c>
       <c r="O5" t="n">
-        <v>8.218116525286069</v>
+        <v>8.192191114686894</v>
       </c>
       <c r="P5" t="n">
-        <v>418.2653695065431</v>
+        <v>418.3181771507953</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12447,28 +12539,28 @@
         <v>0.0429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.400231030954426</v>
+        <v>-1.402206901016824</v>
       </c>
       <c r="J6" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K6" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6232317069368782</v>
+        <v>0.6277063738148434</v>
       </c>
       <c r="M6" t="n">
-        <v>6.733638896523554</v>
+        <v>6.688223065950541</v>
       </c>
       <c r="N6" t="n">
-        <v>74.96848394465032</v>
+        <v>74.37961126982349</v>
       </c>
       <c r="O6" t="n">
-        <v>8.658434266346909</v>
+        <v>8.624361499254508</v>
       </c>
       <c r="P6" t="n">
-        <v>412.1966915853964</v>
+        <v>412.2158232474996</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12525,28 +12617,28 @@
         <v>0.0467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.179515242982283</v>
+        <v>-1.182951487654629</v>
       </c>
       <c r="J7" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K7" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5648660725723084</v>
+        <v>0.5701714849957793</v>
       </c>
       <c r="M7" t="n">
-        <v>6.383154025238567</v>
+        <v>6.346070161791912</v>
       </c>
       <c r="N7" t="n">
-        <v>67.78585779804085</v>
+        <v>67.28592706598782</v>
       </c>
       <c r="O7" t="n">
-        <v>8.233216734547977</v>
+        <v>8.202799952820245</v>
       </c>
       <c r="P7" t="n">
-        <v>402.2032068564927</v>
+        <v>402.236481235526</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12603,28 +12695,28 @@
         <v>0.0453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9737039070847274</v>
+        <v>-0.9776434125914343</v>
       </c>
       <c r="J8" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K8" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L8" t="n">
-        <v>0.441475159680732</v>
+        <v>0.4473441866251436</v>
       </c>
       <c r="M8" t="n">
-        <v>6.565863804323994</v>
+        <v>6.528611473543556</v>
       </c>
       <c r="N8" t="n">
-        <v>75.86554305732086</v>
+        <v>75.31379691281666</v>
       </c>
       <c r="O8" t="n">
-        <v>8.710082838717486</v>
+        <v>8.678352200321019</v>
       </c>
       <c r="P8" t="n">
-        <v>409.1808024386548</v>
+        <v>409.2189553139626</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12681,28 +12773,28 @@
         <v>0.0442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5612844804661888</v>
+        <v>-0.5630199071791409</v>
       </c>
       <c r="J9" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K9" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2457353344152055</v>
+        <v>0.2499160423169167</v>
       </c>
       <c r="M9" t="n">
-        <v>6.054835228859977</v>
+        <v>6.015347504925015</v>
       </c>
       <c r="N9" t="n">
-        <v>61.16130562809265</v>
+        <v>60.68255882814059</v>
       </c>
       <c r="O9" t="n">
-        <v>7.820569392831486</v>
+        <v>7.789901079483654</v>
       </c>
       <c r="P9" t="n">
-        <v>402.6458845539578</v>
+        <v>402.6626801830042</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12740,7 +12832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J247"/>
+  <dimension ref="A1:J249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25583,6 +25675,110 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-35.171628861413176,173.0953681063934</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>-35.171954301244234,173.09617525090067</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>-35.172383751263645,173.0968543848268</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-35.172758164034725,173.09759492695358</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-35.17307268953287,173.09837016009902</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-35.17314220678226,173.09924901791123</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-35.17304511924855,173.10012778141058</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-35.17285753801115,173.10097810320448</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-35.17162345166894,173.09537304905973</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>-35.1719448423229,173.09618330598582</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>-35.17237908677845,173.09685750086933</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-35.17274569260236,173.09760101372683</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-35.173068166821025,173.09837117443112</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-35.1731354459067,173.09924921847713</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-35.17304107728215,173.10012734625155</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-35.17284727230064,173.10097565979262</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0060/nzd0060.xlsx
+++ b/data/nzd0060/nzd0060.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J249"/>
+  <dimension ref="A1:J251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9406,6 +9406,78 @@
       <c r="J249" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="C250" t="n">
+        <v>399.75</v>
+      </c>
+      <c r="D250" t="n">
+        <v>393.05</v>
+      </c>
+      <c r="E250" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="F250" t="n">
+        <v>373.78</v>
+      </c>
+      <c r="G250" t="n">
+        <v>368.89</v>
+      </c>
+      <c r="H250" t="n">
+        <v>380.71</v>
+      </c>
+      <c r="I250" t="n">
+        <v>387.33</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>385.42</v>
+      </c>
+      <c r="C251" t="n">
+        <v>399.34</v>
+      </c>
+      <c r="D251" t="n">
+        <v>393.21</v>
+      </c>
+      <c r="E251" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="F251" t="n">
+        <v>374.49</v>
+      </c>
+      <c r="G251" t="n">
+        <v>369.21</v>
+      </c>
+      <c r="H251" t="n">
+        <v>380.97</v>
+      </c>
+      <c r="I251" t="n">
+        <v>387.36</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:B264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12043,6 +12115,26 @@
       </c>
       <c r="B262" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -12211,28 +12303,28 @@
         <v>0.0403</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09962410646825093</v>
+        <v>-0.1053275001755937</v>
       </c>
       <c r="J2" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K2" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02138701261371401</v>
+        <v>0.02412012559964183</v>
       </c>
       <c r="M2" t="n">
-        <v>4.025025447908035</v>
+        <v>4.021522399669801</v>
       </c>
       <c r="N2" t="n">
-        <v>28.96612292836646</v>
+        <v>28.86294697525672</v>
       </c>
       <c r="O2" t="n">
-        <v>5.382018480864447</v>
+        <v>5.372424683069714</v>
       </c>
       <c r="P2" t="n">
-        <v>391.9427998577145</v>
+        <v>391.9982567753223</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12293,28 +12385,28 @@
         <v>0.0251</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1017114595120385</v>
+        <v>-0.1124892360691016</v>
       </c>
       <c r="J3" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K3" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01498301750440145</v>
+        <v>0.01836606647904915</v>
       </c>
       <c r="M3" t="n">
-        <v>4.977944732917074</v>
+        <v>4.989087979613696</v>
       </c>
       <c r="N3" t="n">
-        <v>43.37953030056408</v>
+        <v>43.49062679986606</v>
       </c>
       <c r="O3" t="n">
-        <v>6.586313862895093</v>
+        <v>6.594742360385738</v>
       </c>
       <c r="P3" t="n">
-        <v>409.9212285957875</v>
+        <v>410.0260351229141</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12375,28 +12467,28 @@
         <v>0.0251</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4379495207167112</v>
+        <v>-0.4492525144093388</v>
       </c>
       <c r="J4" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K4" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1802150370339336</v>
+        <v>0.1889715255154345</v>
       </c>
       <c r="M4" t="n">
-        <v>5.960469949246783</v>
+        <v>5.971877394894471</v>
       </c>
       <c r="N4" t="n">
-        <v>55.79221423236456</v>
+        <v>55.84661451072679</v>
       </c>
       <c r="O4" t="n">
-        <v>7.469418600692062</v>
+        <v>7.473059247104012</v>
       </c>
       <c r="P4" t="n">
-        <v>412.8409638994842</v>
+        <v>412.9505984420954</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -12457,28 +12549,28 @@
         <v>0.0307</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.154701000263527</v>
+        <v>-1.159192861565016</v>
       </c>
       <c r="J5" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K5" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5589241383786843</v>
+        <v>0.5645255056647287</v>
       </c>
       <c r="M5" t="n">
-        <v>6.392452478858062</v>
+        <v>6.362047526241319</v>
       </c>
       <c r="N5" t="n">
-        <v>67.11199525955489</v>
+        <v>66.65471446673614</v>
       </c>
       <c r="O5" t="n">
-        <v>8.192191114686894</v>
+        <v>8.164233856690789</v>
       </c>
       <c r="P5" t="n">
-        <v>418.3181771507953</v>
+        <v>418.3618546393512</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12539,28 +12631,28 @@
         <v>0.0429</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.402206901016824</v>
+        <v>-1.403060644714389</v>
       </c>
       <c r="J6" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K6" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6277063738148434</v>
+        <v>0.6317506312184247</v>
       </c>
       <c r="M6" t="n">
-        <v>6.688223065950541</v>
+        <v>6.638499094961762</v>
       </c>
       <c r="N6" t="n">
-        <v>74.37961126982349</v>
+        <v>73.78864472978813</v>
       </c>
       <c r="O6" t="n">
-        <v>8.624361499254508</v>
+        <v>8.590031707146844</v>
       </c>
       <c r="P6" t="n">
-        <v>412.2158232474996</v>
+        <v>412.2241191040418</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12617,28 +12709,28 @@
         <v>0.0467</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.182951487654629</v>
+        <v>-1.185169023301845</v>
       </c>
       <c r="J7" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K7" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5701714849957793</v>
+        <v>0.5749763908528448</v>
       </c>
       <c r="M7" t="n">
-        <v>6.346070161791912</v>
+        <v>6.304666283818319</v>
       </c>
       <c r="N7" t="n">
-        <v>67.28592706598782</v>
+        <v>66.76732045230881</v>
       </c>
       <c r="O7" t="n">
-        <v>8.202799952820245</v>
+        <v>8.17112724489766</v>
       </c>
       <c r="P7" t="n">
-        <v>402.236481235526</v>
+        <v>402.2580416787299</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -12695,28 +12787,28 @@
         <v>0.0453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9776434125914343</v>
+        <v>-0.9808142700878799</v>
       </c>
       <c r="J8" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K8" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4473441866251436</v>
+        <v>0.4528204996530575</v>
       </c>
       <c r="M8" t="n">
-        <v>6.528611473543556</v>
+        <v>6.489030308488862</v>
       </c>
       <c r="N8" t="n">
-        <v>75.31379691281666</v>
+        <v>74.75110411869687</v>
       </c>
       <c r="O8" t="n">
-        <v>8.678352200321019</v>
+        <v>8.64587208549241</v>
       </c>
       <c r="P8" t="n">
-        <v>409.2189553139626</v>
+        <v>409.2497865284867</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12773,28 +12865,28 @@
         <v>0.0442</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5630199071791409</v>
+        <v>-0.5634012471698356</v>
       </c>
       <c r="J9" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K9" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2499160423169167</v>
+        <v>0.2532160226000711</v>
       </c>
       <c r="M9" t="n">
-        <v>6.015347504925015</v>
+        <v>5.969244601032588</v>
       </c>
       <c r="N9" t="n">
-        <v>60.68255882814059</v>
+        <v>60.19767775312402</v>
       </c>
       <c r="O9" t="n">
-        <v>7.789901079483654</v>
+        <v>7.75871624388494</v>
       </c>
       <c r="P9" t="n">
-        <v>402.6626801830042</v>
+        <v>402.6663879216771</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -12832,7 +12924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J249"/>
+  <dimension ref="A1:J251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25779,6 +25871,110 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>-35.17162525491704,173.09537140150437</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>-35.171953044981265,173.09617632071678</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>-35.172384937149694,173.09685359261258</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-35.17274887323616,173.09759946139556</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-35.17306798945976,173.09837121420884</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-35.1731341838766,173.09924925591608</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-35.17304107728215,173.10012734625155</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-35.172844882868006,173.10097509106754</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>-35.17162244184998,173.0953739716907</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>-35.171956074791915,173.09617374057197</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>-35.17238367220457,173.0968544376411</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-35.17274770142371,173.0976000333071</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-35.1730616931354,173.09837262631802</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-35.17313129923636,173.09924934149086</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-35.17303874192378,173.10012709482635</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-35.17284461737548,173.10097502787585</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
